--- a/artfynd/A 22449-2026 artfynd.xlsx
+++ b/artfynd/A 22449-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129014755</v>
+        <v>129014754</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582045</v>
+        <v>582044</v>
       </c>
       <c r="R2" t="n">
-        <v>6603198</v>
+        <v>6603197</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>47 inspelningar cia A.b med noterad socialt läte</t>
+          <t>8 registreringar via A.b</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>129014758</v>
       </c>
       <c r="B3" t="n">
-        <v>56607</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129014757</v>
       </c>
       <c r="B4" t="n">
-        <v>56600</v>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129014759</v>
       </c>
       <c r="B5" t="n">
-        <v>56600</v>
+        <v>56823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129014754</v>
+        <v>129014755</v>
       </c>
       <c r="B6" t="n">
-        <v>56607</v>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582044</v>
+        <v>582045</v>
       </c>
       <c r="R6" t="n">
-        <v>6603197</v>
+        <v>6603198</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>8 registreringar via A.b</t>
+          <t>47 inspelningar cia A.b med noterad socialt läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1238,7 @@
         <v>129014753</v>
       </c>
       <c r="B7" t="n">
-        <v>56772</v>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22449-2026 artfynd.xlsx
+++ b/artfynd/A 22449-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014757</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014759</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,8 +1374,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>